--- a/01_AI_Governance_Risk_Compliance/1.3_AI_Readiness_Assessment_Tool/sample_output/SAMPLE_Forms_responses_GT_Bahrain.xlsx
+++ b/01_AI_Governance_Risk_Compliance/1.3_AI_Readiness_Assessment_Tool/sample_output/SAMPLE_Forms_responses_GT_Bahrain.xlsx
@@ -579,22 +579,22 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>[Q5] AI strategy &amp; executive ownership</t>
+          <t>[Q5] AI governance structure &amp; accountability</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>[Q6] Use-case portfolio &amp; value realisation</t>
+          <t>[Q6] AI policy, acceptable use &amp; regulatory compliance</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>[Q7] AI governance structure &amp; accountability</t>
+          <t>[Q7] Responsible-AI guardrails &amp; human oversight</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>[Q8] AI policy, acceptable use &amp; regulatory compliance</t>
+          <t>[Q8] AI incidents, monitoring &amp; assurance</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
@@ -619,51 +619,46 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>[Q13] Responsible-AI guardrails &amp; human oversight</t>
+          <t>[Q13] Securing AI systems</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>[Q14] AI incidents, monitoring &amp; assurance</t>
+          <t>[Q14] Defending against AI-enabled threats</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>[Q15] AI literacy &amp; capability</t>
+          <t>[Q15] AI training, literacy &amp; awareness</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>[Q16] Data governance, quality &amp; privacy for AI</t>
+          <t>[Q16] AI strategy &amp; executive ownership</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>[Q17] AI architecture, integration &amp; monitoring</t>
+          <t>[Q17] Use-case portfolio &amp; value realisation</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>[Q18] Model risk management &amp; validation</t>
+          <t>[Q18] Data governance, quality &amp; privacy for AI</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>[Q19] Securing AI systems</t>
+          <t>[Q19] AI architecture, integration &amp; monitoring</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>[Q20] Defending against AI-enabled threats</t>
+          <t>[Q20] Model risk management &amp; validation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>R-0001</t>
-        </is>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>Grant Thornton Bahrain</t>
@@ -761,77 +756,77 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>C</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>D</t>
         </is>
       </c>
     </row>
@@ -1006,82 +1001,82 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>No defined AI governance; decisions are made ad hoc by individual teams</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>No AI policy; applicable AI regulations have not been identified</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>No responsible-AI guardrails or oversight body</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>No AI incident process or assurance</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>AI risks are not identified or managed</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>No AI risk appetite or risk indicators</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>No inventory; AI risks are not assessed</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>AI vendors and AI features in software are not assessed</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>AI systems are not specifically considered in security controls</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>AI-enabled threats not considered</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>No AI training provided</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>No AI strategy or executive owner; AI adoption is unplanned</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>No process - AI initiatives start ad hoc and value is not tracked</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>No defined AI governance; decisions are made ad hoc by individual teams</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>No AI policy; applicable AI regulations have not been identified</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>AI risks are not identified or managed</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>No AI risk appetite or risk indicators</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>No inventory; AI risks are not assessed</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>AI vendors and AI features in software are not assessed</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>No responsible-AI guardrails or oversight body</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>No AI incident process or assurance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>No AI training provided</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Data used by AI is not classified or controlled; privacy requirements not considered</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>No architectural standards; AI solutions built or bought in isolation</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Models are not validated or inventoried</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>AI systems are not specifically considered in security controls</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>AI-enabled threats not considered</t>
         </is>
       </c>
     </row>
@@ -1153,82 +1148,82 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>Informal oversight by IT or a single function; roles not documented</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Informal guidance only (e.g., emails); obligations understood by a few individuals</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>High-level ethical principles published but not operationalised</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>AI issues handled through general IT incident processes; no AI-specific assurance</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>AI risks considered informally within general IT or project risk</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Enterprise risk appetite exists but does not address AI</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Partial list of AI tools; risks assessed occasionally through general IT or vendor processes</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Standard IT procurement only; AI-specific risks not considered</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Standard IT security controls apply; no AI-specific threat assessment</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>General awareness only; no specific controls</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Ad hoc awareness sessions or self-learning only</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>Informal leadership interest; no documented strategy</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Some use cases discussed informally; business cases are rare</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Informal oversight by IT or a single function; roles not documented</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Informal guidance only (e.g., emails); obligations understood by a few individuals</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>AI risks considered informally within general IT or project risk</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Enterprise risk appetite exists but does not address AI</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Partial list of AI tools; risks assessed occasionally through general IT or vendor processes</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Standard IT procurement only; AI-specific risks not considered</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>High-level ethical principles published but not operationalised</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>AI issues handled through general IT incident processes; no AI-specific assurance</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Ad hoc awareness sessions or self-learning only</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Data classification policy exists but is not applied to AI; privacy reviewed case by case</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Some technical guidance exists; monitoring limited to availability</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Developers test their own models; no independent review</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Standard IT security controls apply; no AI-specific threat assessment</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>General awareness only; no specific controls</t>
         </is>
       </c>
     </row>
@@ -1275,82 +1270,82 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>AI committee or sponsor defined on paper; roles and decision rights partly documented</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>AI acceptable-use policy approved; regulatory obligations identified but not mapped to controls</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>AI committee / CoE established; guardrails defined for some areas (e.g., human review of outputs)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>AI incident categories and escalation defined; ad hoc reviews of AI controls</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>AI risk methodology drafted (taxonomy, scales) and applied to some AI initiatives</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>AI risk appetite drafted; a few indicators tracked informally</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AI register with owners; risk assessments performed for some AI systems using a documented method</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>AI questions added to vendor due diligence for some purchases; contract terms vary</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>AI-specific threats (e.g., prompt injection, data leakage) assessed for some systems; access controls and logging in place</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Threat intelligence covers AI-enabled attacks; out-of-band verification for some high-risk requests</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Baseline AI literacy training available to all staff; limited role-based training</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>Executive sponsor named and AI strategy drafted, but not linked to business objectives or budget</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Use-case intake exists and initiatives are prioritised, but benefits are not systematically tracked</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>AI committee or sponsor defined on paper; roles and decision rights partly documented</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>AI acceptable-use policy approved; regulatory obligations identified but not mapped to controls</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>AI risk methodology drafted (taxonomy, scales) and applied to some AI initiatives</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>AI risk appetite drafted; a few indicators tracked informally</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>AI register with owners; risk assessments performed for some AI systems using a documented method</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>AI questions added to vendor due diligence for some purchases; contract terms vary</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>AI committee / CoE established; guardrails defined for some areas (e.g., human review of outputs)</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>AI incident categories and escalation defined; ad hoc reviews of AI controls</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Baseline AI literacy training available to all staff; limited role-based training</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Classification and handling rules apply to AI; DPIAs performed for some AI using personal data</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Reference architecture drafted; approved platforms and integration patterns for most AI; basic performance monitoring</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Model inventory exists; validation performed for some material models</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>AI-specific threats (e.g., prompt injection, data leakage) assessed for some systems; access controls and logging in place</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Threat intelligence covers AI-enabled attacks; out-of-band verification for some high-risk requests</t>
         </is>
       </c>
     </row>
@@ -1387,82 +1382,82 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>Board / ExCo oversight, AI committee with charter and decision rights, named system owners and a documented RACI across the three lines</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>AI policy enforced with staff acknowledgement; obligations register maps regulations to controls and owners</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Guardrails for fairness, transparency, disclosure and human-in-charge controls applied to all relevant AI; committee approves high-risk uses</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>AI incident management with regulatory notification criteria; periodic internal audit of AI governance; assurance obtained from AI vendors</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Approved AI risk framework aligned to ISO/IEC 23894 / NIST AI RMF, applied to all AI use cases and integrated with the enterprise risk register</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Board-approved AI risk appetite with tolerances; KRIs with thresholds monitored and reported at least quarterly</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Complete AI register; all AI use cases risk-tiered and assessed (incl. third-party AI) with approvals proportionate to risk</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mandatory AI due diligence and standard AI contract clauses for all AI vendors; providers reviewed annually</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Secure AI development lifecycle; least privilege for users, systems and agents; sandboxed tool execution; AI red teaming before release; runtime guardrails and audit logging</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Deepfake-resilient verification for payments and sensitive requests; behaviour-based detection; AI incident playbooks exercised</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Mandatory AI literacy before tool access; role-based pathways for developers, oversight staff and leaders; scenario-based security awareness</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>Approved AI strategy with executive ownership, priorities, budget and experimentation boundaries communicated to staff</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Structured intake and prioritisation by value, feasibility, data readiness and risk; KPIs tracked for major initiatives</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Board / ExCo oversight, AI committee with charter and decision rights, named system owners and a documented RACI across the three lines</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>AI policy enforced with staff acknowledgement; obligations register maps regulations to controls and owners</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Approved AI risk framework aligned to ISO/IEC 23894 / NIST AI RMF, applied to all AI use cases and integrated with the enterprise risk register</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Board-approved AI risk appetite with tolerances; KRIs with thresholds monitored and reported at least quarterly</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Complete AI register; all AI use cases risk-tiered and assessed (incl. third-party AI) with approvals proportionate to risk</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Mandatory AI due diligence and standard AI contract clauses for all AI vendors; providers reviewed annually</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Guardrails for fairness, transparency, disclosure and human-in-charge controls applied to all relevant AI; committee approves high-risk uses</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>AI incident management with regulatory notification criteria; periodic internal audit of AI governance; assurance obtained from AI vendors</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Mandatory AI literacy before tool access; role-based pathways for developers, oversight staff and leaders; scenario-based security awareness</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Data readiness assessed before approval; lineage and quality monitored; minimisation, anonymisation and prompt redaction applied; DPIAs standard</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Reference architecture adopted (data, models, agents, security); agent actions via a policy-enforcement gateway; performance, drift and bias monitored with thresholds; kill switches; cost governed</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Independent validation before use and on a risk-based cycle; performance thresholds and limitations documented</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Secure AI development lifecycle; least privilege for users, systems and agents; sandboxed tool execution; AI red teaming before release; runtime guardrails and audit logging</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Deepfake-resilient verification for payments and sensitive requests; behaviour-based detection; AI incident playbooks exercised</t>
         </is>
       </c>
     </row>
@@ -1499,82 +1494,82 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Governance operates effectively: regular board reporting, periodic effectiveness review and independent assurance by internal audit</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Policy and obligations register reviewed regularly with horizon scanning; compliance tested and audit-ready evidence maintained</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Guardrails tested (bias testing, oversight effectiveness); contestability routes for affected persons; lessons fed back into standards</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Post-incident learning drives improvement; AI management system certified or certification-ready (ISO/IEC 42001); assurance reported to the board</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Framework reviewed annually; AI risk aggregated across the portfolio and used in decisions; treatment effectiveness tested</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>KRIs automated with mandatory responses on breach; appetite reviewed annually and used to steer investment and approvals</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Register reconciled quarterly; impact assessments (ISO/IEC 42005 / FRIA) for high-risk uses; re-assessment on change with KRIs monitored</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Continuous monitoring of AI vendors and model changes; AI bill of materials maintained; exit plans for critical providers</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Continuous adversarial testing, AI supply-chain assurance (model scanning, AI-BOM) and forensic-ready logging integrated with the SOC</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Continuous exposure management and AI-specific red teaming; automated response at machine speed; critical vulnerabilities remediated in days</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Competence measured and refreshed annually; workforce plan addresses future AI skills and job redesign; active AI champions network</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>Strategy reviewed at least annually by the board, linked to business strategy and tracked through KPIs</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Portfolio managed as a whole with quarterly value / risk reviews, stop-or-scale decisions, and shadow-AI demand routed into the governed pipeline</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Governance operates effectively: regular board reporting, periodic effectiveness review and independent assurance by internal audit</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Policy and obligations register reviewed regularly with horizon scanning; compliance tested and audit-ready evidence maintained</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Framework reviewed annually; AI risk aggregated across the portfolio and used in decisions; treatment effectiveness tested</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>KRIs automated with mandatory responses on breach; appetite reviewed annually and used to steer investment and approvals</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Register reconciled quarterly; impact assessments (ISO/IEC 42005 / FRIA) for high-risk uses; re-assessment on change with KRIs monitored</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Continuous monitoring of AI vendors and model changes; AI bill of materials maintained; exit plans for critical providers</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Guardrails tested (bias testing, oversight effectiveness); contestability routes for affected persons; lessons fed back into standards</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Post-incident learning drives improvement; AI management system certified or certification-ready (ISO/IEC 42001); assurance reported to the board</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Competence measured and refreshed annually; workforce plan addresses future AI skills and job redesign; active AI champions network</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Automated quality, lineage and privacy controls across AI pipelines; data-subject rights and cross-border transfers handled for AI systems</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Full observability with KRIs and automated responses; governed path from citizen-developed AI to production; platform and vendor dependencies actively managed</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Model risk management aligned to SR 11-7 / PRA SS1/23 principles, with continuous monitoring and findings tracked to closure</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Continuous adversarial testing, AI supply-chain assurance (model scanning, AI-BOM) and forensic-ready logging integrated with the SOC</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Continuous exposure management and AI-specific red teaming; automated response at machine speed; critical vulnerabilities remediated in days</t>
         </is>
       </c>
     </row>
